--- a/src/test/resources/testdataCMS/CMS_DATA.xlsx
+++ b/src/test/resources/testdataCMS/CMS_DATA.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learn\Automation\Automationorangehrmlive\src\test\resources\testdataCMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C620B8F8-3754-4409-9BAF-2C214D0D8786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639734FC-C654-4416-9C23-B3280442B03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{490F9023-B7EE-41AE-A955-F70AB61ADD8E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{490F9023-B7EE-41AE-A955-F70AB61ADD8E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="AddUser" sheetId="1" r:id="rId1"/>
+    <sheet name="SearchUser" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>EmployeeName</t>
   </si>
@@ -54,6 +55,27 @@
   </si>
   <si>
     <t>Confirm Password</t>
+  </si>
+  <si>
+    <t>employeeName</t>
+  </si>
+  <si>
+    <t>user Role</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>confirm Password</t>
+  </si>
+  <si>
+    <t>Admin</t>
   </si>
 </sst>
 </file>
@@ -101,8 +123,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,4 +488,49 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F28A7C-CDA7-4270-8D9F-1501F73B5A22}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/src/test/resources/testdataCMS/CMS_DATA.xlsx
+++ b/src/test/resources/testdataCMS/CMS_DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learn\Automation\Automationorangehrmlive\src\test\resources\testdataCMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639734FC-C654-4416-9C23-B3280442B03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C186EB7-A208-4190-8097-C54E25A0CE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{490F9023-B7EE-41AE-A955-F70AB61ADD8E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>EmployeeName</t>
   </si>
@@ -60,29 +60,26 @@
     <t>employeeName</t>
   </si>
   <si>
-    <t>user Role</t>
-  </si>
-  <si>
     <t>status</t>
   </si>
   <si>
     <t>username</t>
   </si>
   <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>confirm Password</t>
-  </si>
-  <si>
     <t>Admin</t>
+  </si>
+  <si>
+    <t>Random First Name Random Last Name</t>
+  </si>
+  <si>
+    <t>userRole</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +94,19 @@
     </font>
     <font>
       <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -121,10 +131,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,42 +508,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F28A7C-CDA7-4270-8D9F-1501F73B5A22}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.5546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="3"/>
+    <col min="4" max="4" width="23.77734375" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="3"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="54" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/test/resources/testdataCMS/CMS_DATA.xlsx
+++ b/src/test/resources/testdataCMS/CMS_DATA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learn\Automation\Automationorangehrmlive\src\test\resources\testdataCMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C186EB7-A208-4190-8097-C54E25A0CE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624C048E-EC21-4B2F-9DAB-7148CA70721A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{490F9023-B7EE-41AE-A955-F70AB61ADD8E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{490F9023-B7EE-41AE-A955-F70AB61ADD8E}"/>
   </bookViews>
   <sheets>
     <sheet name="AddUser" sheetId="1" r:id="rId1"/>
@@ -37,25 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>EmployeeName</t>
-  </si>
-  <si>
-    <t>User Role</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Confirm Password</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="25">
   <si>
     <t>employeeName</t>
   </si>
@@ -73,6 +55,63 @@
   </si>
   <si>
     <t>userRole</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>conpassword</t>
+  </si>
+  <si>
+    <t>usertest1</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>usertest0000001</t>
+  </si>
+  <si>
+    <t>usertest000002</t>
+  </si>
+  <si>
+    <t>usertest000003</t>
+  </si>
+  <si>
+    <t>usertest000004</t>
+  </si>
+  <si>
+    <t>usertest000005</t>
+  </si>
+  <si>
+    <t>usertest000006</t>
+  </si>
+  <si>
+    <t>usertest000007</t>
+  </si>
+  <si>
+    <t>usertest000008</t>
+  </si>
+  <si>
+    <t>usertest000009</t>
+  </si>
+  <si>
+    <t>usertest000010</t>
+  </si>
+  <si>
+    <t>usertest000011</t>
   </si>
 </sst>
 </file>
@@ -94,11 +133,6 @@
     </font>
     <font>
       <sz val="14"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -109,6 +143,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,12 +174,14 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,33 +517,260 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE1C7057-7773-4830-95BD-8A3D0C1BFDB5}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="18.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="17.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
+      <c r="E1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>2</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>1</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>2</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -511,39 +780,39 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="3"/>
-    <col min="4" max="4" width="23.77734375" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="19.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="4" max="4" width="23.77734375" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>8</v>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="54" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>9</v>
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdataCMS/CMS_DATA.xlsx
+++ b/src/test/resources/testdataCMS/CMS_DATA.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learn\Automation\Automationorangehrmlive\src\test\resources\testdataCMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624C048E-EC21-4B2F-9DAB-7148CA70721A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48CF114-FCB1-4F7E-8CB9-E40268C4525A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{490F9023-B7EE-41AE-A955-F70AB61ADD8E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{490F9023-B7EE-41AE-A955-F70AB61ADD8E}"/>
   </bookViews>
   <sheets>
     <sheet name="AddUser" sheetId="1" r:id="rId1"/>
-    <sheet name="SearchUser" sheetId="2" r:id="rId2"/>
+    <sheet name="EditUser" sheetId="3" r:id="rId2"/>
+    <sheet name="SearchUser" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
   <si>
     <t>employeeName</t>
   </si>
@@ -81,37 +82,40 @@
     <t>o</t>
   </si>
   <si>
-    <t>usertest0000001</t>
-  </si>
-  <si>
-    <t>usertest000002</t>
-  </si>
-  <si>
-    <t>usertest000003</t>
-  </si>
-  <si>
-    <t>usertest000004</t>
-  </si>
-  <si>
-    <t>usertest000005</t>
-  </si>
-  <si>
-    <t>usertest000006</t>
-  </si>
-  <si>
-    <t>usertest000007</t>
-  </si>
-  <si>
-    <t>usertest000008</t>
-  </si>
-  <si>
-    <t>usertest000009</t>
-  </si>
-  <si>
-    <t>usertest000010</t>
-  </si>
-  <si>
-    <t>usertest000011</t>
+    <t>usertes100000000000</t>
+  </si>
+  <si>
+    <t>usertest0000002</t>
+  </si>
+  <si>
+    <t>usertest0000003</t>
+  </si>
+  <si>
+    <t>usertest0000004</t>
+  </si>
+  <si>
+    <t>usertest0000005</t>
+  </si>
+  <si>
+    <t>usertest0000006</t>
+  </si>
+  <si>
+    <t>usertest0000007</t>
+  </si>
+  <si>
+    <t>usertest0000008</t>
+  </si>
+  <si>
+    <t>usertest0000009</t>
+  </si>
+  <si>
+    <t>usertest0000010</t>
+  </si>
+  <si>
+    <t>usertest0000011</t>
+  </si>
+  <si>
+    <t>usertest1000090000</t>
   </si>
 </sst>
 </file>
@@ -776,6 +780,157 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25CD02F7-8A0A-40F4-A5DB-27AD8B64D626}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F28A7C-CDA7-4270-8D9F-1501F73B5A22}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>

--- a/src/test/resources/testdataCMS/CMS_DATA.xlsx
+++ b/src/test/resources/testdataCMS/CMS_DATA.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learn\Automation\Automationorangehrmlive\src\test\resources\testdataCMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48CF114-FCB1-4F7E-8CB9-E40268C4525A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A966ACB-7A93-4BC9-8FE1-683CA117694A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{490F9023-B7EE-41AE-A955-F70AB61ADD8E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{490F9023-B7EE-41AE-A955-F70AB61ADD8E}"/>
   </bookViews>
   <sheets>
     <sheet name="AddUser" sheetId="1" r:id="rId1"/>
     <sheet name="EditUser" sheetId="3" r:id="rId2"/>
-    <sheet name="SearchUser" sheetId="2" r:id="rId3"/>
+    <sheet name="DeleteUser" sheetId="4" r:id="rId3"/>
+    <sheet name="SearchUser" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
   <si>
     <t>employeeName</t>
   </si>
@@ -116,13 +117,22 @@
   </si>
   <si>
     <t>usertest1000090000</t>
+  </si>
+  <si>
+    <t>autouser0-1775717631442</t>
+  </si>
+  <si>
+    <t>bhavanas</t>
+  </si>
+  <si>
+    <t>Dixit0.06548401522989167</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +164,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF38455D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -175,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -187,6 +203,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -931,6 +949,52 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B99D8D5E-77AE-4761-A70B-6278D3C097CD}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="5"/>
+    </row>
+    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F28A7C-CDA7-4270-8D9F-1501F73B5A22}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
